--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -32248,12 +32248,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -32278,7 +32278,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -32287,81 +32287,100 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -32388,17 +32407,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -32423,7 +32442,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -32432,26 +32451,103 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O183" t="n">
-        <v>0</v>
-      </c>
-      <c r="P183" t="n">
-        <v>0</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0</v>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN183" t="b">
+        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
@@ -32460,7 +32556,7 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ183" t="inlineStr">
@@ -32468,9 +32564,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS183" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT183" t="n">
@@ -32478,47 +32579,47 @@
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -32545,17 +32646,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -32594,168 +32695,76 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="P184" t="n">
-        <v>0</v>
-      </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W184" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y184" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD184" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE184" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF184" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG184" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN184" t="b">
-        <v>1</v>
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32787,12 +32796,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -32817,7 +32826,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -32831,6 +32840,9 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -32839,68 +32851,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32927,7 +32948,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -32962,7 +32983,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -32979,18 +33000,98 @@
       <c r="P186" t="n">
         <v>0</v>
       </c>
-      <c r="R186" t="n">
-        <v>0</v>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN186" t="b">
+        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
@@ -33084,17 +33185,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -33133,168 +33234,76 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="P187" t="n">
-        <v>0</v>
-      </c>
-      <c r="U187" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W187" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y187" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD187" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE187" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF187" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG187" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM187" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN187" t="b">
-        <v>1</v>
+      <c r="R187" t="n">
+        <v>0</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33326,12 +33335,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -33356,7 +33365,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -33370,6 +33379,9 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -33378,68 +33390,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33466,7 +33487,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -33501,7 +33522,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -33518,18 +33539,98 @@
       <c r="P189" t="n">
         <v>0</v>
       </c>
-      <c r="R189" t="n">
-        <v>0</v>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN189" t="b">
+        <v>1</v>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
@@ -33623,17 +33724,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -33672,168 +33773,76 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE190" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF190" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG190" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN190" t="b">
-        <v>1</v>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33865,12 +33874,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -33895,7 +33904,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -33909,6 +33918,9 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -33917,68 +33929,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34005,7 +34026,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -34040,7 +34061,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -34057,18 +34078,98 @@
       <c r="P192" t="n">
         <v>0</v>
       </c>
-      <c r="R192" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN192" t="b">
+        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -34162,17 +34263,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -34211,168 +34312,76 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="P193" t="n">
-        <v>0</v>
-      </c>
-      <c r="U193" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W193" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD193" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE193" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF193" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG193" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN193" t="b">
-        <v>1</v>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34404,12 +34413,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -34434,12 +34443,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N194" t="n">
@@ -34448,6 +34457,9 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -34456,68 +34468,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34544,17 +34565,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -34579,12 +34600,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N195" t="n">
@@ -34593,76 +34614,168 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="R195" t="n">
-        <v>0</v>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN195" t="b">
+        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34694,12 +34807,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -34746,87 +34859,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR196" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -34853,217 +34947,526 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr"/>
+      <c r="AT197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="G199" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>D091</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
         <is>
           <t>肉毒杆菌中毒</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
+      <c r="K199" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
+      <c r="L199" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr">
+      <c r="M199" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N197" t="n">
-        <v>0</v>
-      </c>
-      <c r="O197" t="n">
-        <v>0</v>
-      </c>
-      <c r="U197" t="inlineStr">
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="V197" t="inlineStr">
+      <c r="V199" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="W197" t="inlineStr">
+      <c r="W199" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X197" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>Botulisme</t>
         </is>
       </c>
-      <c r="Y197" t="inlineStr">
+      <c r="Y199" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z197" t="inlineStr">
+      <c r="Z199" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA197" t="inlineStr">
+      <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB197" t="inlineStr">
+      <c r="AB199" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC197" t="inlineStr">
+      <c r="AC199" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD197" t="inlineStr">
+      <c r="AD199" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE197" t="inlineStr">
+      <c r="AE199" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF197" t="inlineStr">
+      <c r="AF199" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG197" t="inlineStr">
+      <c r="AG199" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH197" t="inlineStr">
+      <c r="AH199" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI197" t="inlineStr">
+      <c r="AI199" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ197" t="inlineStr">
+      <c r="AJ199" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK197" t="inlineStr">
+      <c r="AK199" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM197" t="inlineStr">
+      <c r="AM199" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN197" t="b">
+      <c r="AN199" t="b">
         <v>1</v>
       </c>
-      <c r="AO197" t="inlineStr">
+      <c r="AO199" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP197" t="inlineStr">
+      <c r="AP199" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ197" t="inlineStr">
+      <c r="AQ199" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR197" t="inlineStr">
+      <c r="AR199" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS197" t="inlineStr">
+      <c r="AS199" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="AT197" t="n">
+      <c r="AT199" t="n">
         <v>2</v>
       </c>
-      <c r="AU197" t="inlineStr">
+      <c r="AU199" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV197" t="inlineStr">
+      <c r="AV199" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW197" t="inlineStr">
+      <c r="AW199" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX197" t="inlineStr">
+      <c r="AX199" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY197" t="inlineStr">
+      <c r="AY199" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ197" t="inlineStr">
+      <c r="AZ199" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA197" t="inlineStr">
+      <c r="BA199" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB197" t="inlineStr">
+      <c r="BB199" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC197" t="inlineStr">
+      <c r="BC199" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -35185,7 +35588,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
@@ -35195,7 +35598,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -35215,7 +35618,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -35247,7 +35650,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -34807,12 +34807,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -34837,12 +34837,12 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N196" t="n">
@@ -34885,42 +34885,42 @@
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34952,12 +34952,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -35030,42 +35030,42 @@
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35097,12 +35097,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -35149,87 +35149,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR198" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35256,7 +35237,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -35305,98 +35286,23 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U199" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>Botulisme</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG199" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN199" t="b">
-        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -35467,6 +35373,245 @@
         </is>
       </c>
       <c r="BC199" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>Botulisme</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN200" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -35588,7 +35733,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10">
@@ -35598,7 +35743,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -34952,12 +34952,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -34982,12 +34982,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N197" t="n">
@@ -34996,6 +34996,9 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -35004,68 +35007,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35092,17 +35104,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -35127,12 +35139,12 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N198" t="n">
@@ -35141,76 +35153,168 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="R198" t="n">
-        <v>0</v>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN198" t="b">
+        <v>1</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35242,12 +35346,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -35294,87 +35398,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35401,217 +35486,526 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
+      <c r="AT200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
+      <c r="F202" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
+      <c r="G202" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>D091</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
         <is>
           <t>肉毒杆菌中毒</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
+      <c r="K202" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
+      <c r="L202" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr">
+      <c r="M202" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N200" t="n">
-        <v>0</v>
-      </c>
-      <c r="O200" t="n">
-        <v>0</v>
-      </c>
-      <c r="U200" t="inlineStr">
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="U202" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="V200" t="inlineStr">
+      <c r="V202" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="W200" t="inlineStr">
+      <c r="W202" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X200" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>Botulisme</t>
         </is>
       </c>
-      <c r="Y200" t="inlineStr">
+      <c r="Y202" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z200" t="inlineStr">
+      <c r="Z202" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA200" t="inlineStr">
+      <c r="AA202" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB200" t="inlineStr">
+      <c r="AB202" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC200" t="inlineStr">
+      <c r="AC202" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD200" t="inlineStr">
+      <c r="AD202" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE200" t="inlineStr">
+      <c r="AE202" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF200" t="inlineStr">
+      <c r="AF202" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG200" t="inlineStr">
+      <c r="AG202" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH200" t="inlineStr">
+      <c r="AH202" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI200" t="inlineStr">
+      <c r="AI202" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ200" t="inlineStr">
+      <c r="AJ202" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK200" t="inlineStr">
+      <c r="AK202" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM200" t="inlineStr">
+      <c r="AM202" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN200" t="b">
+      <c r="AN202" t="b">
         <v>1</v>
       </c>
-      <c r="AO200" t="inlineStr">
+      <c r="AO202" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP200" t="inlineStr">
+      <c r="AP202" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ200" t="inlineStr">
+      <c r="AQ202" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR200" t="inlineStr">
+      <c r="AR202" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS200" t="inlineStr">
+      <c r="AS202" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="AT200" t="n">
+      <c r="AT202" t="n">
         <v>2</v>
       </c>
-      <c r="AU200" t="inlineStr">
+      <c r="AU202" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV200" t="inlineStr">
+      <c r="AV202" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW200" t="inlineStr">
+      <c r="AW202" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX200" t="inlineStr">
+      <c r="AX202" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY200" t="inlineStr">
+      <c r="AY202" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ200" t="inlineStr">
+      <c r="AZ202" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA200" t="inlineStr">
+      <c r="BA202" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB200" t="inlineStr">
+      <c r="BB202" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC200" t="inlineStr">
+      <c r="BC202" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -35733,7 +36127,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10">
@@ -35743,7 +36137,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -35763,7 +36157,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -27022,12 +27022,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -27066,76 +27066,87 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="R151" t="n">
-        <v>0</v>
-      </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BOTULISM_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BOTULISM_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27162,17 +27173,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -27211,76 +27222,165 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="R152" t="n">
-        <v>0</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BOTULISM_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BOTULISM_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary botulism notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>1</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BOTULISM_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27312,12 +27412,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -27364,87 +27464,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -27471,17 +27552,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -27520,170 +27601,76 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>Botulisme</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN154" t="b">
-        <v>1</v>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR154" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27715,12 +27702,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -27769,7 +27756,7 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -27799,7 +27786,7 @@
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT155" t="n">
@@ -27812,42 +27799,42 @@
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27879,12 +27866,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -27925,22 +27912,22 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>Botulism</t>
+          <t>Botulisme</t>
         </is>
       </c>
       <c r="Y156" t="inlineStr">
@@ -27965,7 +27952,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr">
@@ -28000,17 +27987,17 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -28038,7 +28025,7 @@
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT156" t="n">
@@ -28051,42 +28038,42 @@
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28118,12 +28105,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -28148,7 +28135,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -28170,68 +28157,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28258,17 +28264,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -28293,7 +28299,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -28307,21 +28313,98 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="P158" t="n">
-        <v>0</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0</v>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN158" t="b">
+        <v>1</v>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
@@ -28330,7 +28413,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ158" t="inlineStr">
@@ -28338,9 +28421,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT158" t="n">
@@ -28348,47 +28436,47 @@
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28415,17 +28503,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -28450,7 +28538,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -28464,168 +28552,76 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="P159" t="n">
-        <v>0</v>
-      </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN159" t="b">
-        <v>1</v>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28657,12 +28653,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -28687,7 +28683,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -28701,6 +28697,9 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -28709,68 +28708,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28797,7 +28805,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -28832,7 +28840,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -28849,18 +28857,98 @@
       <c r="P161" t="n">
         <v>0</v>
       </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
+        <v>1</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
@@ -28954,17 +29042,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -28989,7 +29077,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -29003,168 +29091,76 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="P162" t="n">
-        <v>0</v>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>1</v>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29196,12 +29192,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -29226,7 +29222,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -29240,6 +29236,9 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -29248,68 +29247,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29336,7 +29344,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -29371,7 +29379,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -29388,18 +29396,98 @@
       <c r="P164" t="n">
         <v>0</v>
       </c>
-      <c r="R164" t="n">
-        <v>0</v>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN164" t="b">
+        <v>1</v>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
@@ -29493,17 +29581,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -29528,7 +29616,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -29542,168 +29630,76 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="P165" t="n">
-        <v>0</v>
-      </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE165" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN165" t="b">
-        <v>1</v>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29735,12 +29731,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -29765,7 +29761,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -29779,6 +29775,9 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -29787,68 +29786,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29875,17 +29883,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -29910,7 +29918,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -29924,76 +29932,168 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="R167" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30025,12 +30125,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -30055,7 +30155,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -30069,9 +30169,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -30080,77 +30177,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30177,17 +30265,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -30226,168 +30314,76 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="P169" t="n">
-        <v>0</v>
-      </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE169" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF169" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG169" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN169" t="b">
-        <v>1</v>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30419,12 +30415,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -30449,12 +30445,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N170" t="n">
@@ -30463,6 +30459,9 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -30471,68 +30470,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30559,17 +30567,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -30594,12 +30602,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N171" t="n">
@@ -30608,73 +30616,168 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>1</v>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30706,12 +30809,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -30750,9 +30853,12 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -30786,12 +30892,12 @@
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -30806,12 +30912,12 @@
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
@@ -30848,12 +30954,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -30928,7 +31034,7 @@
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
@@ -30948,7 +31054,7 @@
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
@@ -30990,12 +31096,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -31070,7 +31176,7 @@
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
@@ -31090,7 +31196,7 @@
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
@@ -31132,12 +31238,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -31212,7 +31318,7 @@
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
@@ -31232,7 +31338,7 @@
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
@@ -31274,12 +31380,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -31354,7 +31460,7 @@
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
@@ -31374,7 +31480,7 @@
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
@@ -31416,12 +31522,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -31496,7 +31602,7 @@
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
@@ -31516,7 +31622,7 @@
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
@@ -31558,12 +31664,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -31638,7 +31744,7 @@
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
@@ -31658,7 +31764,7 @@
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
@@ -31700,12 +31806,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -31744,12 +31850,9 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="R179" t="n">
-        <v>0</v>
-      </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -31778,42 +31881,42 @@
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31845,12 +31948,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -31889,95 +31992,73 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="R180" t="n">
-        <v>0</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -32004,17 +32085,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -32053,170 +32134,76 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Botulisme</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>1</v>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR181" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -32248,12 +32235,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -32287,13 +32274,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>0.009344880428283346</v>
+        <v>0</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -32302,7 +32289,7 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -32332,7 +32319,7 @@
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT182" t="n">
@@ -32345,42 +32332,42 @@
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -32412,12 +32399,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -32451,29 +32438,29 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>Botulism</t>
+          <t>Botulisme</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
@@ -32498,7 +32485,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD183" t="inlineStr">
@@ -32533,17 +32520,17 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -32571,7 +32558,7 @@
       </c>
       <c r="AS183" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT183" t="n">
@@ -32584,42 +32571,42 @@
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -32651,12 +32638,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -32681,7 +32668,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -32690,81 +32677,100 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -32791,17 +32797,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -32826,7 +32832,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -32835,26 +32841,103 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O185" t="n">
-        <v>0</v>
-      </c>
-      <c r="P185" t="n">
-        <v>0</v>
-      </c>
-      <c r="R185" t="n">
-        <v>0</v>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN185" t="b">
+        <v>1</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
@@ -32863,7 +32946,7 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ185" t="inlineStr">
@@ -32871,9 +32954,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT185" t="n">
@@ -32881,47 +32969,47 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -32948,17 +33036,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -32997,168 +33085,76 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="P186" t="n">
-        <v>0</v>
-      </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA186" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN186" t="b">
-        <v>1</v>
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33190,12 +33186,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -33220,7 +33216,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -33234,6 +33230,9 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -33242,68 +33241,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33330,7 +33338,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -33365,7 +33373,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -33382,18 +33390,98 @@
       <c r="P188" t="n">
         <v>0</v>
       </c>
-      <c r="R188" t="n">
-        <v>0</v>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN188" t="b">
+        <v>1</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
@@ -33487,17 +33575,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -33536,168 +33624,76 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="P189" t="n">
-        <v>0</v>
-      </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W189" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y189" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD189" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE189" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF189" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG189" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN189" t="b">
-        <v>1</v>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33729,12 +33725,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -33759,7 +33755,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -33773,6 +33769,9 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -33781,68 +33780,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33869,7 +33877,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -33904,7 +33912,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -33921,18 +33929,98 @@
       <c r="P191" t="n">
         <v>0</v>
       </c>
-      <c r="R191" t="n">
-        <v>0</v>
-      </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN191" t="b">
+        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
@@ -34026,17 +34114,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -34075,168 +34163,76 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="P192" t="n">
-        <v>0</v>
-      </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA192" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN192" t="b">
-        <v>1</v>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34268,12 +34264,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -34298,7 +34294,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -34312,6 +34308,9 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -34320,68 +34319,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34408,7 +34416,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -34443,7 +34451,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -34460,18 +34468,98 @@
       <c r="P194" t="n">
         <v>0</v>
       </c>
-      <c r="R194" t="n">
-        <v>0</v>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -34565,17 +34653,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -34614,168 +34702,76 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="P195" t="n">
-        <v>0</v>
-      </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN195" t="b">
-        <v>1</v>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34807,12 +34803,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -34837,7 +34833,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -34851,6 +34847,9 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -34859,68 +34858,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34947,7 +34955,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -34982,7 +34990,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -34999,18 +35007,98 @@
       <c r="P197" t="n">
         <v>0</v>
       </c>
-      <c r="R197" t="n">
-        <v>0</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
@@ -35104,17 +35192,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -35153,168 +35241,76 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="P198" t="n">
-        <v>0</v>
-      </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN198" t="b">
-        <v>1</v>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35346,12 +35342,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -35376,12 +35372,12 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N199" t="n">
@@ -35390,6 +35386,9 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -35398,68 +35397,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35486,17 +35494,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -35521,12 +35529,12 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N200" t="n">
@@ -35535,76 +35543,168 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="R200" t="n">
-        <v>0</v>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN200" t="b">
+        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35636,12 +35736,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35688,87 +35788,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35795,217 +35876,526 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr"/>
+      <c r="AT202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA203" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F204" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G204" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>D091</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
         <is>
           <t>肉毒杆菌中毒</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="K204" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="L204" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr">
+      <c r="M204" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N202" t="n">
-        <v>0</v>
-      </c>
-      <c r="O202" t="n">
-        <v>0</v>
-      </c>
-      <c r="U202" t="inlineStr">
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="U204" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="V202" t="inlineStr">
+      <c r="V204" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="W202" t="inlineStr">
+      <c r="W204" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X202" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>Botulisme</t>
         </is>
       </c>
-      <c r="Y202" t="inlineStr">
+      <c r="Y204" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z202" t="inlineStr">
+      <c r="Z204" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA202" t="inlineStr">
+      <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB202" t="inlineStr">
+      <c r="AB204" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC202" t="inlineStr">
+      <c r="AC204" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD202" t="inlineStr">
+      <c r="AD204" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE202" t="inlineStr">
+      <c r="AE204" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF202" t="inlineStr">
+      <c r="AF204" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG202" t="inlineStr">
+      <c r="AG204" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH202" t="inlineStr">
+      <c r="AH204" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI202" t="inlineStr">
+      <c r="AI204" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ202" t="inlineStr">
+      <c r="AJ204" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK202" t="inlineStr">
+      <c r="AK204" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM202" t="inlineStr">
+      <c r="AM204" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN202" t="b">
+      <c r="AN204" t="b">
         <v>1</v>
       </c>
-      <c r="AO202" t="inlineStr">
+      <c r="AO204" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP202" t="inlineStr">
+      <c r="AP204" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ202" t="inlineStr">
+      <c r="AQ204" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR202" t="inlineStr">
+      <c r="AR204" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS202" t="inlineStr">
+      <c r="AS204" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="AT202" t="n">
+      <c r="AT204" t="n">
         <v>2</v>
       </c>
-      <c r="AU202" t="inlineStr">
+      <c r="AU204" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV202" t="inlineStr">
+      <c r="AV204" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW202" t="inlineStr">
+      <c r="AW204" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX202" t="inlineStr">
+      <c r="AX204" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY202" t="inlineStr">
+      <c r="AY204" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ202" t="inlineStr">
+      <c r="AZ204" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA202" t="inlineStr">
+      <c r="BA204" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB202" t="inlineStr">
+      <c r="BB204" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC202" t="inlineStr">
+      <c r="BC204" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -36127,7 +36517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
@@ -36137,7 +36527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -36157,7 +36547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -36401,6 +36401,151 @@
         </is>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
+      <c r="AT205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV205" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA205" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB205" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC205" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36434,7 +36579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -36517,7 +36662,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10">
@@ -36527,7 +36672,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -36546,6 +36546,400 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" t="n">
+        <v>0</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
+      <c r="AT206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA206" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB206" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC206" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
+      <c r="AT207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA207" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36662,7 +37056,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
@@ -36672,7 +37066,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -36692,7 +37086,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -32090,12 +32090,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -32168,42 +32168,42 @@
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -32235,12 +32235,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -32287,87 +32287,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -32394,7 +32375,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -32443,98 +32424,23 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>Botulisme</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN183" t="b">
-        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
@@ -32633,17 +32539,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -32677,29 +32583,104 @@
         </is>
       </c>
       <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Botulisme</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN184" t="b">
         <v>1</v>
       </c>
-      <c r="O184" t="n">
-        <v>1</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0.009344880428283346</v>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
-        </is>
-      </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -32722,7 +32703,7 @@
       </c>
       <c r="AS184" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT184" t="n">
@@ -32735,42 +32716,42 @@
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -32797,7 +32778,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -32846,98 +32827,23 @@
       <c r="O185" t="n">
         <v>1</v>
       </c>
+      <c r="R185" t="n">
+        <v>0.009344880428283346</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U185" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W185" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y185" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD185" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE185" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF185" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG185" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN185" t="b">
-        <v>1</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
@@ -33036,17 +32942,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -33071,7 +32977,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -33080,81 +32986,175 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O186" t="n">
-        <v>0</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0</v>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN186" t="b">
+        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR186" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -33186,12 +33186,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -33230,9 +33230,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="P187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -33241,77 +33238,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33338,7 +33326,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -33390,98 +33378,18 @@
       <c r="P188" t="n">
         <v>0</v>
       </c>
-      <c r="U188" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W188" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y188" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD188" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE188" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF188" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG188" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH188" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ188" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM188" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN188" t="b">
-        <v>1</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
@@ -33575,17 +33483,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -33610,7 +33518,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -33624,76 +33532,168 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="R189" t="n">
-        <v>0</v>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN189" t="b">
+        <v>1</v>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33725,12 +33725,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -33769,9 +33769,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -33780,77 +33777,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33877,7 +33865,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -33929,98 +33917,18 @@
       <c r="P191" t="n">
         <v>0</v>
       </c>
-      <c r="U191" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V191" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W191" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y191" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R191" t="n">
+        <v>0</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD191" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE191" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF191" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG191" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN191" t="b">
-        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
@@ -34114,17 +34022,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -34149,7 +34057,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -34163,76 +34071,168 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="R192" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN192" t="b">
+        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34264,12 +34264,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -34308,9 +34308,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="P193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -34319,77 +34316,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34416,7 +34404,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -34468,98 +34456,18 @@
       <c r="P194" t="n">
         <v>0</v>
       </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN194" t="b">
-        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -34653,17 +34561,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -34688,7 +34596,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -34702,76 +34610,168 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="R195" t="n">
-        <v>0</v>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN195" t="b">
+        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34803,12 +34803,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -34847,9 +34847,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="P196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -34858,77 +34855,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34955,7 +34943,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -35007,98 +34995,18 @@
       <c r="P197" t="n">
         <v>0</v>
       </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD197" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE197" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF197" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN197" t="b">
-        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
@@ -35192,17 +35100,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -35227,7 +35135,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -35241,76 +35149,168 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="R198" t="n">
-        <v>0</v>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN198" t="b">
+        <v>1</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35342,12 +35342,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -35386,9 +35386,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="P199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -35397,77 +35394,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35494,7 +35482,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -35546,98 +35534,18 @@
       <c r="P200" t="n">
         <v>0</v>
       </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
@@ -35731,17 +35639,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35766,12 +35674,12 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N201" t="n">
@@ -35780,76 +35688,168 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="R201" t="n">
-        <v>0</v>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
+        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35881,12 +35881,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -35959,42 +35959,42 @@
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -36026,12 +36026,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -36078,87 +36078,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR203" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -36185,7 +36166,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -36234,98 +36215,23 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U204" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Botulisme</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
@@ -36424,17 +36330,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -36459,7 +36365,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -36473,76 +36379,170 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="R205" t="n">
-        <v>0</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Botulisme</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR205" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -36574,12 +36574,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -36618,9 +36618,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="P206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -36629,77 +36626,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36726,7 +36714,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -36778,98 +36766,18 @@
       <c r="P207" t="n">
         <v>0</v>
       </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD207" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE207" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG207" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ207" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM207" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN207" t="b">
-        <v>1</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
@@ -36935,6 +36843,782 @@
         </is>
       </c>
       <c r="BC207" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN208" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
+      <c r="AT208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
+      <c r="AT209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
+      <c r="AT210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA210" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
+      <c r="AT211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -36973,7 +37657,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -37056,7 +37740,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
@@ -37066,7 +37750,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -37086,7 +37770,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -37624,6 +37624,690 @@
         </is>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr"/>
+      <c r="AT212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
+      <c r="AT213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN214" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
+      <c r="AT214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU214" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV214" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA214" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB214" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC214" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr"/>
+      <c r="AT215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV215" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB215" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC215" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37657,7 +38341,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -37740,7 +38424,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
@@ -37750,7 +38434,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -37770,7 +38454,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -27997,7 +27997,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -32675,7 +32675,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -36466,7 +36466,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -63070,6 +63070,151 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N383" t="n">
+        <v>0</v>
+      </c>
+      <c r="O383" t="n">
+        <v>0</v>
+      </c>
+      <c r="R383" t="n">
+        <v>0</v>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO383" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP383" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR383" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS383" t="inlineStr"/>
+      <c r="AT383" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU383" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV383" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW383" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX383" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY383" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA383" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB383" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC383" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -63103,7 +63248,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -63186,7 +63331,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -63196,7 +63341,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11">
